--- a/sources/3E_Manha_1_Bimestre.xlsx
+++ b/sources/3E_Manha_1_Bimestre.xlsx
@@ -255,6 +255,15 @@
     <x:t>83%</x:t>
   </x:si>
   <x:si>
+    <x:t>DANIELA RAMOS MIRANDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0%</x:t>
+  </x:si>
+  <x:si>
     <x:t>DOMINGOS VICTOR LUZOLO JOAO</x:t>
   </x:si>
   <x:si>
@@ -273,6 +282,9 @@
     <x:t>46%</x:t>
   </x:si>
   <x:si>
+    <x:t>ELOISE DE CARVALHO GONCALVES</x:t>
+  </x:si>
+  <x:si>
     <x:t>EMANUELLY LORRAINE DE ASSIS DE OLIVEIRA</x:t>
   </x:si>
   <x:si>
@@ -429,12 +441,24 @@
     <x:t>44%</x:t>
   </x:si>
   <x:si>
+    <x:t>MARIANE DUARTE SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Transferido</x:t>
+  </x:si>
+  <x:si>
     <x:t>MATHEUS ARTHUR FROTA DOS SANTOS</x:t>
   </x:si>
   <x:si>
+    <x:t>MATHEUS DOS SANTOS GENIAL LIMA</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOISES BATISTA VIEIRA</x:t>
   </x:si>
   <x:si>
+    <x:t>NICOLAS MARCON MARQUES</x:t>
+  </x:si>
+  <x:si>
     <x:t>NICOLE NOGUEIRA DAMIAO</x:t>
   </x:si>
   <x:si>
@@ -474,6 +498,12 @@
     <x:t>55%</x:t>
   </x:si>
   <x:si>
+    <x:t>RYAN GUEDES DE BRITO FRANCISCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98%</x:t>
+  </x:si>
+  <x:si>
     <x:t>RYAN SOARES AQUINO</x:t>
   </x:si>
   <x:si>
@@ -489,46 +519,19 @@
     <x:t>70%</x:t>
   </x:si>
   <x:si>
+    <x:t>VINICIUS ALVES ROCHA</x:t>
+  </x:si>
+  <x:si>
     <x:t>VINICIUS GIMENEZ DA COSTA</x:t>
   </x:si>
   <x:si>
-    <x:t>98%</x:t>
-  </x:si>
-  <x:si>
     <x:t>WENDEL RAMOS DELFINO DE SOUZA</x:t>
   </x:si>
   <x:si>
+    <x:t>YUMI EUGENIO URATA</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZION KALUEMBI SANTOS PORTELA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUMI EUGENIO URATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYAN GUEDES DE BRITO FRANCISCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NICOLAS MARCON MARQUES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DANIELA RAMOS MIRANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELOISE DE CARVALHO GONCALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MATHEUS DOS SANTOS GENIAL LIMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VINICIUS ALVES ROCHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIANE DUARTE SOUZA</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> </x:t>
@@ -2246,7 +2249,7 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B17" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C17" s="12">
         <x:v>5</x:v>
@@ -2255,10 +2258,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E17" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G17" s="12">
         <x:v>5</x:v>
@@ -2267,10 +2270,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I17" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K17" s="12">
         <x:v>5</x:v>
@@ -2279,10 +2282,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="M17" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O17" s="12">
         <x:v>5</x:v>
@@ -2291,10 +2294,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="Q17" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="R17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="S17" s="12">
         <x:v>5</x:v>
@@ -2303,10 +2306,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="U17" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="W17" s="12">
         <x:v>5</x:v>
@@ -2315,10 +2318,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="Y17" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AA17" s="12">
         <x:v>5</x:v>
@@ -2327,10 +2330,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AC17" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AE17" s="12">
         <x:v>5</x:v>
@@ -2339,10 +2342,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AG17" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AI17" s="12">
         <x:v>5</x:v>
@@ -2351,10 +2354,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AK17" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AM17" s="12">
         <x:v>5</x:v>
@@ -2363,10 +2366,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AO17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AP17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AQ17" s="12">
         <x:v>5</x:v>
@@ -2375,10 +2378,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AS17" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AU17" s="12">
         <x:v>5</x:v>
@@ -2387,10 +2390,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AW17" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AY17" s="12">
         <x:v>5</x:v>
@@ -2399,10 +2402,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="BA17" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BB17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BC17" s="12">
         <x:v>5</x:v>
@@ -2411,39 +2414,39 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="BE17" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BF17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BG17" s="12">
-        <x:v>171</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH17" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI17" s="12">
-        <x:v>171</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BJ17" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:62">
       <x:c r="A18" s="11" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D18" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E18" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F18" s="12" t="s">
         <x:v>49</x:v>
@@ -2452,10 +2455,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="H18" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I18" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J18" s="12" t="s">
         <x:v>49</x:v>
@@ -2464,10 +2467,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="L18" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M18" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N18" s="12" t="s">
         <x:v>49</x:v>
@@ -2476,10 +2479,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="P18" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q18" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R18" s="12" t="s">
         <x:v>49</x:v>
@@ -2488,22 +2491,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="T18" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U18" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="V18" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="X18" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y18" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Z18" s="12" t="s">
         <x:v>49</x:v>
@@ -2512,10 +2515,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AB18" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC18" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AD18" s="12" t="s">
         <x:v>49</x:v>
@@ -2524,10 +2527,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AF18" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG18" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AH18" s="12" t="s">
         <x:v>49</x:v>
@@ -2536,10 +2539,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AJ18" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK18" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AL18" s="12" t="s">
         <x:v>49</x:v>
@@ -2548,7 +2551,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AN18" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO18" s="12" t="s">
         <x:v>48</x:v>
@@ -2560,10 +2563,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AR18" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS18" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AT18" s="12" t="s">
         <x:v>49</x:v>
@@ -2572,10 +2575,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AV18" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW18" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AX18" s="12" t="s">
         <x:v>49</x:v>
@@ -2584,10 +2587,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AZ18" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BA18" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BB18" s="12" t="s">
         <x:v>49</x:v>
@@ -2596,7 +2599,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="BD18" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE18" s="12" t="s">
         <x:v>61</x:v>
@@ -2605,21 +2608,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG18" s="12">
-        <x:v>172</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="BH18" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="BI18" s="12">
-        <x:v>158</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="BJ18" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:62">
       <x:c r="A19" s="11" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B19" s="12" t="s">
         <x:v>47</x:v>
@@ -2628,198 +2631,198 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F19" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="H19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J19" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="L19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M19" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N19" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="P19" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="R19" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="S19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="T19" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="W19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="X19" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z19" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AA19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AB19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC19" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD19" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AE19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AF19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG19" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH19" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AI19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AJ19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL19" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AM19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AN19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO19" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AP19" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AQ19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AR19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT19" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AU19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AV19" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX19" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AY19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AZ19" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BA19" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BB19" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BC19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="BD19" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BF19" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BG19" s="12">
-        <x:v>62</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH19" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI19" s="12">
-        <x:v>54</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BJ19" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:62">
       <x:c r="A20" s="11" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E20" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F20" s="12" t="s">
         <x:v>49</x:v>
@@ -2828,10 +2831,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H20" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I20" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="J20" s="12" t="s">
         <x:v>49</x:v>
@@ -2840,10 +2843,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="L20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M20" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N20" s="12" t="s">
         <x:v>49</x:v>
@@ -2852,10 +2855,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="P20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q20" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="R20" s="12" t="s">
         <x:v>49</x:v>
@@ -2864,13 +2867,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="T20" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U20" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="V20" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="W20" s="12">
         <x:v>8</x:v>
@@ -2879,7 +2882,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="Y20" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="Z20" s="12" t="s">
         <x:v>49</x:v>
@@ -2888,10 +2891,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AB20" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD20" s="12" t="s">
         <x:v>49</x:v>
@@ -2900,10 +2903,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AF20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG20" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="AH20" s="12" t="s">
         <x:v>49</x:v>
@@ -2912,10 +2915,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AJ20" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="AL20" s="12" t="s">
         <x:v>49</x:v>
@@ -2927,7 +2930,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AO20" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP20" s="12" t="s">
         <x:v>49</x:v>
@@ -2936,10 +2939,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AR20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS20" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AT20" s="12" t="s">
         <x:v>49</x:v>
@@ -2948,10 +2951,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AV20" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW20" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AX20" s="12" t="s">
         <x:v>49</x:v>
@@ -2960,10 +2963,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AZ20" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BA20" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BB20" s="12" t="s">
         <x:v>49</x:v>
@@ -2972,42 +2975,42 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="BD20" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BE20" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BF20" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG20" s="12">
-        <x:v>57</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="BH20" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="BI20" s="12">
-        <x:v>57</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="BJ20" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:62">
       <x:c r="A21" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D21" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F21" s="12" t="s">
         <x:v>49</x:v>
@@ -3016,10 +3019,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="H21" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I21" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J21" s="12" t="s">
         <x:v>49</x:v>
@@ -3028,7 +3031,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="L21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M21" s="12" t="s">
         <x:v>54</x:v>
@@ -3043,7 +3046,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Q21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R21" s="12" t="s">
         <x:v>49</x:v>
@@ -3052,22 +3055,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="T21" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="W21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="X21" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Z21" s="12" t="s">
         <x:v>49</x:v>
@@ -3076,10 +3079,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AB21" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC21" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD21" s="12" t="s">
         <x:v>49</x:v>
@@ -3088,10 +3091,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AF21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG21" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH21" s="12" t="s">
         <x:v>49</x:v>
@@ -3100,10 +3103,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AJ21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK21" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL21" s="12" t="s">
         <x:v>49</x:v>
@@ -3112,10 +3115,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AN21" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP21" s="12" t="s">
         <x:v>49</x:v>
@@ -3127,7 +3130,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AS21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AT21" s="12" t="s">
         <x:v>49</x:v>
@@ -3139,7 +3142,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AW21" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX21" s="12" t="s">
         <x:v>49</x:v>
@@ -3151,7 +3154,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BA21" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BB21" s="12" t="s">
         <x:v>49</x:v>
@@ -3160,30 +3163,30 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="BD21" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="BE21" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="BF21" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="BG21" s="12">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="BE21" s="12" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="BF21" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="BG21" s="12">
-        <x:v>122</x:v>
-      </x:c>
       <x:c r="BH21" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BI21" s="12">
-        <x:v>112</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BJ21" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:62">
       <x:c r="A22" s="11" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
         <x:v>47</x:v>
@@ -3192,7 +3195,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D22" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
         <x:v>52</x:v>
@@ -3204,10 +3207,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I22" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J22" s="12" t="s">
         <x:v>49</x:v>
@@ -3216,7 +3219,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L22" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M22" s="12" t="s">
         <x:v>52</x:v>
@@ -3240,22 +3243,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="T22" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U22" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="V22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="X22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y22" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z22" s="12" t="s">
         <x:v>49</x:v>
@@ -3264,10 +3267,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AB22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AC22" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD22" s="12" t="s">
         <x:v>49</x:v>
@@ -3276,10 +3279,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AF22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH22" s="12" t="s">
         <x:v>49</x:v>
@@ -3288,10 +3291,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AJ22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK22" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL22" s="12" t="s">
         <x:v>49</x:v>
@@ -3315,7 +3318,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AS22" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT22" s="12" t="s">
         <x:v>49</x:v>
@@ -3324,10 +3327,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AV22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW22" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX22" s="12" t="s">
         <x:v>49</x:v>
@@ -3336,7 +3339,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AZ22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA22" s="12" t="s">
         <x:v>67</x:v>
@@ -3348,7 +3351,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="BD22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BE22" s="12" t="s">
         <x:v>55</x:v>
@@ -3357,33 +3360,33 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG22" s="12">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BH22" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="BI22" s="12">
-        <x:v>33</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BJ22" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:62">
       <x:c r="A23" s="11" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F23" s="12" t="s">
         <x:v>49</x:v>
@@ -3392,10 +3395,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="H23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J23" s="12" t="s">
         <x:v>49</x:v>
@@ -3404,10 +3407,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="L23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M23" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N23" s="12" t="s">
         <x:v>49</x:v>
@@ -3416,10 +3419,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="P23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R23" s="12" t="s">
         <x:v>49</x:v>
@@ -3428,22 +3431,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="T23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="W23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="X23" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z23" s="12" t="s">
         <x:v>49</x:v>
@@ -3452,10 +3455,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AB23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD23" s="12" t="s">
         <x:v>49</x:v>
@@ -3464,10 +3467,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AF23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AH23" s="12" t="s">
         <x:v>49</x:v>
@@ -3476,10 +3479,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AJ23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK23" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL23" s="12" t="s">
         <x:v>49</x:v>
@@ -3488,10 +3491,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AN23" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP23" s="12" t="s">
         <x:v>49</x:v>
@@ -3500,10 +3503,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AR23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT23" s="12" t="s">
         <x:v>49</x:v>
@@ -3512,10 +3515,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AV23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AX23" s="12" t="s">
         <x:v>49</x:v>
@@ -3524,10 +3527,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AZ23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA23" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BB23" s="12" t="s">
         <x:v>49</x:v>
@@ -3536,30 +3539,30 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="BD23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BE23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="BF23" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG23" s="12">
-        <x:v>50</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="BH23" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="BI23" s="12">
-        <x:v>48</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BJ23" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:62">
       <x:c r="A24" s="11" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
         <x:v>47</x:v>
@@ -3568,10 +3571,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D24" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E24" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F24" s="12" t="s">
         <x:v>49</x:v>
@@ -3580,10 +3583,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H24" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I24" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J24" s="12" t="s">
         <x:v>49</x:v>
@@ -3592,7 +3595,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="L24" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M24" s="12" t="s">
         <x:v>52</x:v>
@@ -3604,10 +3607,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="P24" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q24" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R24" s="12" t="s">
         <x:v>49</x:v>
@@ -3616,19 +3619,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="T24" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U24" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V24" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="W24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="X24" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y24" s="12" t="s">
         <x:v>52</x:v>
@@ -3643,7 +3646,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AC24" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AD24" s="12" t="s">
         <x:v>49</x:v>
@@ -3652,10 +3655,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AF24" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AG24" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH24" s="12" t="s">
         <x:v>49</x:v>
@@ -3664,10 +3667,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AJ24" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK24" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL24" s="12" t="s">
         <x:v>49</x:v>
@@ -3679,7 +3682,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AO24" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP24" s="12" t="s">
         <x:v>49</x:v>
@@ -3688,7 +3691,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AR24" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS24" s="12" t="s">
         <x:v>52</x:v>
@@ -3700,10 +3703,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AV24" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW24" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX24" s="12" t="s">
         <x:v>49</x:v>
@@ -3712,10 +3715,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AZ24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA24" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BB24" s="12" t="s">
         <x:v>49</x:v>
@@ -3724,30 +3727,30 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="BD24" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE24" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF24" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG24" s="12">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="BH24" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BI24" s="12">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="BJ24" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:62">
       <x:c r="A25" s="11" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
         <x:v>47</x:v>
@@ -3756,10 +3759,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E25" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F25" s="12" t="s">
         <x:v>49</x:v>
@@ -3771,7 +3774,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I25" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J25" s="12" t="s">
         <x:v>49</x:v>
@@ -3780,7 +3783,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="L25" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M25" s="12" t="s">
         <x:v>67</x:v>
@@ -3792,10 +3795,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="P25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R25" s="12" t="s">
         <x:v>49</x:v>
@@ -3804,7 +3807,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="T25" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U25" s="12" t="s">
         <x:v>52</x:v>
@@ -3816,10 +3819,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="X25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z25" s="12" t="s">
         <x:v>49</x:v>
@@ -3828,10 +3831,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AB25" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC25" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD25" s="12" t="s">
         <x:v>49</x:v>
@@ -3843,7 +3846,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AG25" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH25" s="12" t="s">
         <x:v>49</x:v>
@@ -3852,10 +3855,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AJ25" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK25" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL25" s="12" t="s">
         <x:v>49</x:v>
@@ -3876,7 +3879,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AR25" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS25" s="12" t="s">
         <x:v>52</x:v>
@@ -3888,10 +3891,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AV25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW25" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX25" s="12" t="s">
         <x:v>49</x:v>
@@ -3912,10 +3915,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="BD25" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE25" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BF25" s="12" t="s">
         <x:v>49</x:v>
@@ -3924,18 +3927,18 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BH25" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="BI25" s="12">
         <x:v>48</x:v>
       </x:c>
       <x:c r="BJ25" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:62">
       <x:c r="A26" s="11" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
         <x:v>47</x:v>
@@ -3944,10 +3947,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F26" s="12" t="s">
         <x:v>49</x:v>
@@ -3956,10 +3959,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="H26" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J26" s="12" t="s">
         <x:v>49</x:v>
@@ -3968,7 +3971,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="L26" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M26" s="12" t="s">
         <x:v>52</x:v>
@@ -3983,7 +3986,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Q26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R26" s="12" t="s">
         <x:v>49</x:v>
@@ -3992,7 +3995,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="T26" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U26" s="12" t="s">
         <x:v>54</x:v>
@@ -4004,10 +4007,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="X26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y26" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Z26" s="12" t="s">
         <x:v>49</x:v>
@@ -4016,10 +4019,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AB26" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD26" s="12" t="s">
         <x:v>49</x:v>
@@ -4028,10 +4031,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AF26" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG26" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH26" s="12" t="s">
         <x:v>49</x:v>
@@ -4040,7 +4043,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AJ26" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK26" s="12" t="s">
         <x:v>55</x:v>
@@ -4055,7 +4058,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AO26" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP26" s="12" t="s">
         <x:v>49</x:v>
@@ -4064,10 +4067,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AR26" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS26" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AT26" s="12" t="s">
         <x:v>49</x:v>
@@ -4076,7 +4079,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AV26" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW26" s="12" t="s">
         <x:v>52</x:v>
@@ -4088,10 +4091,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AZ26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA26" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BB26" s="12" t="s">
         <x:v>49</x:v>
@@ -4100,7 +4103,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="BD26" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BE26" s="12" t="s">
         <x:v>54</x:v>
@@ -4109,16 +4112,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG26" s="12">
-        <x:v>84</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="BH26" s="12" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BI26" s="12">
-        <x:v>80</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="BJ26" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:62">
@@ -4132,10 +4135,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D27" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E27" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F27" s="12" t="s">
         <x:v>49</x:v>
@@ -4144,10 +4147,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="H27" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I27" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J27" s="12" t="s">
         <x:v>49</x:v>
@@ -4156,10 +4159,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M27" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N27" s="12" t="s">
         <x:v>49</x:v>
@@ -4168,10 +4171,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="P27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q27" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R27" s="12" t="s">
         <x:v>49</x:v>
@@ -4180,22 +4183,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="T27" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="V27" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="W27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="X27" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y27" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z27" s="12" t="s">
         <x:v>49</x:v>
@@ -4204,10 +4207,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AB27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AD27" s="12" t="s">
         <x:v>49</x:v>
@@ -4216,10 +4219,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AF27" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AH27" s="12" t="s">
         <x:v>49</x:v>
@@ -4228,10 +4231,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AJ27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK27" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AL27" s="12" t="s">
         <x:v>49</x:v>
@@ -4240,10 +4243,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AN27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO27" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP27" s="12" t="s">
         <x:v>49</x:v>
@@ -4252,10 +4255,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AR27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AT27" s="12" t="s">
         <x:v>49</x:v>
@@ -4264,10 +4267,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AV27" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX27" s="12" t="s">
         <x:v>49</x:v>
@@ -4276,10 +4279,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AZ27" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA27" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BB27" s="12" t="s">
         <x:v>49</x:v>
@@ -4288,30 +4291,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="BD27" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BE27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BF27" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG27" s="12">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BH27" s="12" t="s">
-        <x:v>105</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="BI27" s="12">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BJ27" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:62">
       <x:c r="A28" s="11" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
         <x:v>47</x:v>
@@ -4320,10 +4323,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E28" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F28" s="12" t="s">
         <x:v>49</x:v>
@@ -4332,10 +4335,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H28" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J28" s="12" t="s">
         <x:v>49</x:v>
@@ -4344,10 +4347,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="L28" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M28" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N28" s="12" t="s">
         <x:v>49</x:v>
@@ -4359,7 +4362,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Q28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R28" s="12" t="s">
         <x:v>49</x:v>
@@ -4368,22 +4371,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="T28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="W28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="X28" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="Y28" s="12" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="Y28" s="12" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="Z28" s="12" t="s">
         <x:v>49</x:v>
@@ -4395,7 +4398,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AC28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD28" s="12" t="s">
         <x:v>49</x:v>
@@ -4404,10 +4407,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AF28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AG28" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AH28" s="12" t="s">
         <x:v>49</x:v>
@@ -4416,10 +4419,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AJ28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AL28" s="12" t="s">
         <x:v>49</x:v>
@@ -4431,7 +4434,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AO28" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP28" s="12" t="s">
         <x:v>49</x:v>
@@ -4440,10 +4443,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AR28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AS28" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AT28" s="12" t="s">
         <x:v>49</x:v>
@@ -4452,7 +4455,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AV28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW28" s="12" t="s">
         <x:v>52</x:v>
@@ -4464,10 +4467,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AZ28" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA28" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB28" s="12" t="s">
         <x:v>49</x:v>
@@ -4476,30 +4479,30 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="BD28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE28" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BF28" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG28" s="12">
-        <x:v>62</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="BH28" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BI28" s="12">
-        <x:v>54</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="BJ28" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:62">
       <x:c r="A29" s="11" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B29" s="12" t="s">
         <x:v>47</x:v>
@@ -4508,10 +4511,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F29" s="12" t="s">
         <x:v>49</x:v>
@@ -4520,7 +4523,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I29" s="12" t="s">
         <x:v>52</x:v>
@@ -4532,7 +4535,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="L29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M29" s="12" t="s">
         <x:v>62</x:v>
@@ -4544,10 +4547,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R29" s="12" t="s">
         <x:v>49</x:v>
@@ -4559,19 +4562,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="W29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="X29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y29" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Z29" s="12" t="s">
         <x:v>49</x:v>
@@ -4592,10 +4595,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AF29" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AG29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AH29" s="12" t="s">
         <x:v>49</x:v>
@@ -4604,7 +4607,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AJ29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK29" s="12" t="s">
         <x:v>57</x:v>
@@ -4616,10 +4619,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AN29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AO29" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP29" s="12" t="s">
         <x:v>49</x:v>
@@ -4628,10 +4631,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AR29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AS29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT29" s="12" t="s">
         <x:v>49</x:v>
@@ -4640,10 +4643,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AV29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW29" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX29" s="12" t="s">
         <x:v>49</x:v>
@@ -4652,7 +4655,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AZ29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA29" s="12" t="s">
         <x:v>62</x:v>
@@ -4664,7 +4667,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="BD29" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BE29" s="12" t="s">
         <x:v>48</x:v>
@@ -4673,21 +4676,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG29" s="12">
-        <x:v>76</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BH29" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BI29" s="12">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BJ29" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:62">
       <x:c r="A30" s="11" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
         <x:v>47</x:v>
@@ -4696,10 +4699,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D30" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F30" s="12" t="s">
         <x:v>49</x:v>
@@ -4708,10 +4711,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J30" s="12" t="s">
         <x:v>49</x:v>
@@ -4723,7 +4726,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="M30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N30" s="12" t="s">
         <x:v>49</x:v>
@@ -4735,7 +4738,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Q30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R30" s="12" t="s">
         <x:v>49</x:v>
@@ -4747,19 +4750,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U30" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V30" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="W30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="X30" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Z30" s="12" t="s">
         <x:v>49</x:v>
@@ -4771,7 +4774,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AC30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD30" s="12" t="s">
         <x:v>49</x:v>
@@ -4780,10 +4783,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AF30" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG30" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AH30" s="12" t="s">
         <x:v>49</x:v>
@@ -4795,7 +4798,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AK30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL30" s="12" t="s">
         <x:v>49</x:v>
@@ -4804,10 +4807,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AN30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP30" s="12" t="s">
         <x:v>49</x:v>
@@ -4816,10 +4819,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AR30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT30" s="12" t="s">
         <x:v>49</x:v>
@@ -4831,7 +4834,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AW30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX30" s="12" t="s">
         <x:v>49</x:v>
@@ -4840,10 +4843,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AZ30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BA30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BB30" s="12" t="s">
         <x:v>49</x:v>
@@ -4855,22 +4858,22 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BE30" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF30" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG30" s="12">
-        <x:v>11</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BH30" s="12" t="s">
-        <x:v>110</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BI30" s="12">
-        <x:v>9</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BJ30" s="12" t="s">
-        <x:v>110</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:62">
@@ -4884,10 +4887,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F31" s="12" t="s">
         <x:v>49</x:v>
@@ -4896,10 +4899,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H31" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J31" s="12" t="s">
         <x:v>49</x:v>
@@ -4911,7 +4914,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="M31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N31" s="12" t="s">
         <x:v>49</x:v>
@@ -4920,10 +4923,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="P31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q31" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R31" s="12" t="s">
         <x:v>49</x:v>
@@ -4935,19 +4938,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="W31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="X31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y31" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z31" s="12" t="s">
         <x:v>49</x:v>
@@ -4956,22 +4959,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AB31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC31" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD31" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AF31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH31" s="12" t="s">
         <x:v>49</x:v>
@@ -4983,7 +4986,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AK31" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AL31" s="12" t="s">
         <x:v>49</x:v>
@@ -4995,7 +4998,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AO31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP31" s="12" t="s">
         <x:v>49</x:v>
@@ -5007,7 +5010,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AS31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AT31" s="12" t="s">
         <x:v>49</x:v>
@@ -5016,10 +5019,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AV31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AX31" s="12" t="s">
         <x:v>49</x:v>
@@ -5028,10 +5031,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AZ31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA31" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BB31" s="12" t="s">
         <x:v>49</x:v>
@@ -5040,30 +5043,30 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="BD31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BE31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF31" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG31" s="12">
-        <x:v>31</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BH31" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="BI31" s="12">
-        <x:v>23</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="BJ31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:62">
       <x:c r="A32" s="11" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
         <x:v>47</x:v>
@@ -5072,10 +5075,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F32" s="12" t="s">
         <x:v>49</x:v>
@@ -5084,7 +5087,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I32" s="12" t="s">
         <x:v>49</x:v>
@@ -5108,10 +5111,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="P32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R32" s="12" t="s">
         <x:v>49</x:v>
@@ -5120,7 +5123,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="T32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U32" s="12" t="s">
         <x:v>52</x:v>
@@ -5132,7 +5135,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="X32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y32" s="12" t="s">
         <x:v>49</x:v>
@@ -5144,7 +5147,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AB32" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC32" s="12" t="s">
         <x:v>49</x:v>
@@ -5156,7 +5159,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AF32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG32" s="12" t="s">
         <x:v>52</x:v>
@@ -5168,10 +5171,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AJ32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL32" s="12" t="s">
         <x:v>49</x:v>
@@ -5180,10 +5183,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AN32" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP32" s="12" t="s">
         <x:v>49</x:v>
@@ -5192,7 +5195,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AR32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS32" s="12" t="s">
         <x:v>49</x:v>
@@ -5204,7 +5207,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AV32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW32" s="12" t="s">
         <x:v>49</x:v>
@@ -5216,7 +5219,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AZ32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA32" s="12" t="s">
         <x:v>49</x:v>
@@ -5228,7 +5231,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="BD32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BE32" s="12" t="s">
         <x:v>52</x:v>
@@ -5237,21 +5240,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG32" s="12">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="BH32" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="BI32" s="12">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="BJ32" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:62">
       <x:c r="A33" s="11" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B33" s="12" t="s">
         <x:v>47</x:v>
@@ -5260,7 +5263,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E33" s="12" t="s">
         <x:v>49</x:v>
@@ -5272,10 +5275,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I33" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J33" s="12" t="s">
         <x:v>49</x:v>
@@ -5284,7 +5287,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="L33" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M33" s="12" t="s">
         <x:v>49</x:v>
@@ -5296,10 +5299,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="P33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R33" s="12" t="s">
         <x:v>49</x:v>
@@ -5308,13 +5311,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="T33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="W33" s="12">
         <x:v>21</x:v>
@@ -5323,7 +5326,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Y33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Z33" s="12" t="s">
         <x:v>49</x:v>
@@ -5332,22 +5335,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AB33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AE33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="AF33" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AG33" s="12" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="AG33" s="12" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="AH33" s="12" t="s">
         <x:v>49</x:v>
@@ -5359,7 +5362,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AK33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL33" s="12" t="s">
         <x:v>49</x:v>
@@ -5392,7 +5395,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AV33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW33" s="12" t="s">
         <x:v>49</x:v>
@@ -5404,10 +5407,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AZ33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BA33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BB33" s="12" t="s">
         <x:v>49</x:v>
@@ -5416,25 +5419,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="BD33" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BE33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF33" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG33" s="12">
-        <x:v>2</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="BH33" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="BI33" s="12">
-        <x:v>2</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="BJ33" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:62">
@@ -5448,10 +5451,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="D34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F34" s="12" t="s">
         <x:v>49</x:v>
@@ -5460,10 +5463,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H34" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J34" s="12" t="s">
         <x:v>49</x:v>
@@ -5472,10 +5475,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="L34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M34" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N34" s="12" t="s">
         <x:v>49</x:v>
@@ -5484,10 +5487,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="P34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R34" s="12" t="s">
         <x:v>49</x:v>
@@ -5496,22 +5499,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="T34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="V34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="W34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="X34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y34" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z34" s="12" t="s">
         <x:v>49</x:v>
@@ -5520,10 +5523,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AB34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AC34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD34" s="12" t="s">
         <x:v>49</x:v>
@@ -5532,10 +5535,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AF34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AG34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH34" s="12" t="s">
         <x:v>49</x:v>
@@ -5544,10 +5547,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AJ34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK34" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL34" s="12" t="s">
         <x:v>49</x:v>
@@ -5559,7 +5562,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AO34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP34" s="12" t="s">
         <x:v>49</x:v>
@@ -5568,10 +5571,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AR34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT34" s="12" t="s">
         <x:v>49</x:v>
@@ -5580,10 +5583,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AV34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX34" s="12" t="s">
         <x:v>49</x:v>
@@ -5592,10 +5595,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AZ34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BA34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB34" s="12" t="s">
         <x:v>49</x:v>
@@ -5604,30 +5607,30 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="BD34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BE34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BF34" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG34" s="12">
-        <x:v>65</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="BH34" s="12" t="s">
-        <x:v>105</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="BI34" s="12">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="BJ34" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:62">
       <x:c r="A35" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
         <x:v>47</x:v>
@@ -5639,7 +5642,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F35" s="12" t="s">
         <x:v>49</x:v>
@@ -5651,7 +5654,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I35" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J35" s="12" t="s">
         <x:v>49</x:v>
@@ -5660,7 +5663,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="L35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M35" s="12" t="s">
         <x:v>49</x:v>
@@ -5672,10 +5675,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="P35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R35" s="12" t="s">
         <x:v>49</x:v>
@@ -5684,22 +5687,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="T35" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U35" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V35" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="X35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z35" s="12" t="s">
         <x:v>49</x:v>
@@ -5711,7 +5714,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AC35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD35" s="12" t="s">
         <x:v>49</x:v>
@@ -5723,7 +5726,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AG35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH35" s="12" t="s">
         <x:v>49</x:v>
@@ -5735,7 +5738,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AK35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL35" s="12" t="s">
         <x:v>49</x:v>
@@ -5747,7 +5750,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AO35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP35" s="12" t="s">
         <x:v>49</x:v>
@@ -5768,7 +5771,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AV35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW35" s="12" t="s">
         <x:v>49</x:v>
@@ -5780,10 +5783,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AZ35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA35" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB35" s="12" t="s">
         <x:v>49</x:v>
@@ -5795,19 +5798,19 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="BE35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF35" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG35" s="12">
-        <x:v>45</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BH35" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="BI35" s="12">
-        <x:v>39</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BJ35" s="12" t="s">
         <x:v>119</x:v>
@@ -5824,10 +5827,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F36" s="12" t="s">
         <x:v>49</x:v>
@@ -5836,10 +5839,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I36" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J36" s="12" t="s">
         <x:v>49</x:v>
@@ -5848,10 +5851,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="L36" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M36" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N36" s="12" t="s">
         <x:v>49</x:v>
@@ -5860,10 +5863,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="P36" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q36" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R36" s="12" t="s">
         <x:v>49</x:v>
@@ -5872,13 +5875,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="T36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="W36" s="12">
         <x:v>24</x:v>
@@ -5887,7 +5890,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="Y36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Z36" s="12" t="s">
         <x:v>49</x:v>
@@ -5896,10 +5899,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AB36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC36" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD36" s="12" t="s">
         <x:v>49</x:v>
@@ -5908,10 +5911,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AF36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG36" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH36" s="12" t="s">
         <x:v>49</x:v>
@@ -5920,10 +5923,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AJ36" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK36" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="AL36" s="12" t="s">
         <x:v>49</x:v>
@@ -5932,10 +5935,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AN36" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP36" s="12" t="s">
         <x:v>49</x:v>
@@ -5944,10 +5947,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AR36" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT36" s="12" t="s">
         <x:v>49</x:v>
@@ -5956,10 +5959,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AV36" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX36" s="12" t="s">
         <x:v>49</x:v>
@@ -5968,10 +5971,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AZ36" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BA36" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB36" s="12" t="s">
         <x:v>49</x:v>
@@ -5980,30 +5983,30 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="BD36" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BE36" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BF36" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG36" s="12">
-        <x:v>110</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BH36" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BI36" s="12">
-        <x:v>107</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BJ36" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:62">
       <x:c r="A37" s="11" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B37" s="12" t="s">
         <x:v>47</x:v>
@@ -6012,10 +6015,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D37" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
         <x:v>49</x:v>
@@ -6036,7 +6039,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M37" s="12" t="s">
         <x:v>49</x:v>
@@ -6048,10 +6051,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="P37" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q37" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R37" s="12" t="s">
         <x:v>49</x:v>
@@ -6072,10 +6075,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="X37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Z37" s="12" t="s">
         <x:v>49</x:v>
@@ -6087,7 +6090,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AC37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD37" s="12" t="s">
         <x:v>49</x:v>
@@ -6096,10 +6099,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AF37" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AG37" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH37" s="12" t="s">
         <x:v>49</x:v>
@@ -6111,7 +6114,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AK37" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL37" s="12" t="s">
         <x:v>49</x:v>
@@ -6123,7 +6126,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AO37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP37" s="12" t="s">
         <x:v>49</x:v>
@@ -6144,7 +6147,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AV37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW37" s="12" t="s">
         <x:v>49</x:v>
@@ -6168,25 +6171,25 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="BD37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BE37" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF37" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG37" s="12">
-        <x:v>19</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="BH37" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="BI37" s="12">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="BJ37" s="12" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="BI37" s="12">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="BJ37" s="12" t="s">
-        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:62">
@@ -6194,16 +6197,16 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F38" s="12" t="s">
         <x:v>49</x:v>
@@ -6212,10 +6215,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="H38" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J38" s="12" t="s">
         <x:v>49</x:v>
@@ -6227,7 +6230,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="M38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N38" s="12" t="s">
         <x:v>49</x:v>
@@ -6236,10 +6239,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="P38" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R38" s="12" t="s">
         <x:v>49</x:v>
@@ -6251,19 +6254,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U38" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="V38" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="W38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="X38" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y38" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z38" s="12" t="s">
         <x:v>49</x:v>
@@ -6272,10 +6275,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AB38" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AC38" s="12" t="s">
-        <x:v>125</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="AD38" s="12" t="s">
         <x:v>49</x:v>
@@ -6287,7 +6290,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="AG38" s="12" t="s">
-        <x:v>126</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AH38" s="12" t="s">
         <x:v>49</x:v>
@@ -6296,10 +6299,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AJ38" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK38" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL38" s="12" t="s">
         <x:v>49</x:v>
@@ -6308,7 +6311,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AN38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AO38" s="12" t="s">
         <x:v>53</x:v>
@@ -6323,7 +6326,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AS38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT38" s="12" t="s">
         <x:v>49</x:v>
@@ -6332,10 +6335,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AV38" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW38" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX38" s="12" t="s">
         <x:v>49</x:v>
@@ -6347,7 +6350,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="BA38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BB38" s="12" t="s">
         <x:v>49</x:v>
@@ -6356,30 +6359,30 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="BD38" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BE38" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF38" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG38" s="12">
-        <x:v>165</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="BH38" s="12" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="BI38" s="12">
-        <x:v>153</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BJ38" s="12" t="s">
-        <x:v>129</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:62">
       <x:c r="A39" s="11" t="s">
-        <x:v>130</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
         <x:v>47</x:v>
@@ -6388,10 +6391,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F39" s="12" t="s">
         <x:v>49</x:v>
@@ -6400,10 +6403,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="H39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I39" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J39" s="12" t="s">
         <x:v>49</x:v>
@@ -6412,7 +6415,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="L39" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M39" s="12" t="s">
         <x:v>49</x:v>
@@ -6424,10 +6427,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="P39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q39" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R39" s="12" t="s">
         <x:v>49</x:v>
@@ -6439,19 +6442,19 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="U39" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V39" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="W39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="X39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z39" s="12" t="s">
         <x:v>49</x:v>
@@ -6460,10 +6463,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AB39" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD39" s="12" t="s">
         <x:v>49</x:v>
@@ -6472,10 +6475,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AF39" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG39" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AH39" s="12" t="s">
         <x:v>49</x:v>
@@ -6484,10 +6487,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AJ39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL39" s="12" t="s">
         <x:v>49</x:v>
@@ -6508,7 +6511,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AR39" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS39" s="12" t="s">
         <x:v>49</x:v>
@@ -6520,10 +6523,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AV39" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX39" s="12" t="s">
         <x:v>49</x:v>
@@ -6532,10 +6535,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AZ39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA39" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BB39" s="12" t="s">
         <x:v>49</x:v>
@@ -6544,42 +6547,42 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="BD39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE39" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF39" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG39" s="12">
-        <x:v>56</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="BH39" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="BI39" s="12">
-        <x:v>54</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="BJ39" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:62">
       <x:c r="A40" s="11" t="s">
-        <x:v>131</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="D40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
         <x:v>49</x:v>
@@ -6588,10 +6591,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="H40" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I40" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J40" s="12" t="s">
         <x:v>49</x:v>
@@ -6600,10 +6603,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="L40" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N40" s="12" t="s">
         <x:v>49</x:v>
@@ -6612,10 +6615,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="P40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Q40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R40" s="12" t="s">
         <x:v>49</x:v>
@@ -6630,7 +6633,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="V40" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="W40" s="12">
         <x:v>28</x:v>
@@ -6639,7 +6642,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="Y40" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="Z40" s="12" t="s">
         <x:v>49</x:v>
@@ -6648,10 +6651,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AB40" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC40" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="AD40" s="12" t="s">
         <x:v>49</x:v>
@@ -6663,7 +6666,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="AG40" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="AH40" s="12" t="s">
         <x:v>49</x:v>
@@ -6672,10 +6675,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AJ40" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AK40" s="12" t="s">
-        <x:v>126</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AL40" s="12" t="s">
         <x:v>49</x:v>
@@ -6687,7 +6690,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AO40" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AP40" s="12" t="s">
         <x:v>49</x:v>
@@ -6696,10 +6699,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AR40" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AS40" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AT40" s="12" t="s">
         <x:v>49</x:v>
@@ -6711,7 +6714,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="AW40" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AX40" s="12" t="s">
         <x:v>49</x:v>
@@ -6723,7 +6726,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="BA40" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BB40" s="12" t="s">
         <x:v>49</x:v>
@@ -6735,27 +6738,27 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="BE40" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="BF40" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG40" s="12">
-        <x:v>179</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="BH40" s="12" t="s">
         <x:v>132</x:v>
       </x:c>
       <x:c r="BI40" s="12">
-        <x:v>179</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="BJ40" s="12" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:62">
       <x:c r="A41" s="11" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
         <x:v>47</x:v>
@@ -6764,10 +6767,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F41" s="12" t="s">
         <x:v>49</x:v>
@@ -6779,7 +6782,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J41" s="12" t="s">
         <x:v>49</x:v>
@@ -6791,7 +6794,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="M41" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N41" s="12" t="s">
         <x:v>49</x:v>
@@ -6803,7 +6806,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Q41" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R41" s="12" t="s">
         <x:v>49</x:v>
@@ -6812,22 +6815,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="T41" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="V41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="W41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="X41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z41" s="12" t="s">
         <x:v>49</x:v>
@@ -6836,10 +6839,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AB41" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD41" s="12" t="s">
         <x:v>49</x:v>
@@ -6848,10 +6851,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AF41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH41" s="12" t="s">
         <x:v>49</x:v>
@@ -6860,10 +6863,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AJ41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK41" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL41" s="12" t="s">
         <x:v>49</x:v>
@@ -6875,7 +6878,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AO41" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP41" s="12" t="s">
         <x:v>49</x:v>
@@ -6884,10 +6887,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AR41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS41" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT41" s="12" t="s">
         <x:v>49</x:v>
@@ -6896,10 +6899,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AV41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX41" s="12" t="s">
         <x:v>49</x:v>
@@ -6908,10 +6911,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AZ41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA41" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB41" s="12" t="s">
         <x:v>49</x:v>
@@ -6920,33 +6923,33 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="BD41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BE41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BF41" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG41" s="12">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BH41" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="BI41" s="12">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BJ41" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:62">
       <x:c r="A42" s="11" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B42" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C42" s="12">
         <x:v>30</x:v>
@@ -6955,7 +6958,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F42" s="12" t="s">
         <x:v>49</x:v>
@@ -6964,10 +6967,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H42" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I42" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J42" s="12" t="s">
         <x:v>49</x:v>
@@ -6976,10 +6979,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="M42" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N42" s="12" t="s">
         <x:v>49</x:v>
@@ -6988,10 +6991,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="P42" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="R42" s="12" t="s">
         <x:v>49</x:v>
@@ -7000,22 +7003,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="T42" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="X42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Z42" s="12" t="s">
         <x:v>49</x:v>
@@ -7027,7 +7030,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AC42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="AD42" s="12" t="s">
         <x:v>49</x:v>
@@ -7036,10 +7039,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AF42" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AG42" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="AH42" s="12" t="s">
         <x:v>49</x:v>
@@ -7048,10 +7051,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AJ42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AK42" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="AL42" s="12" t="s">
         <x:v>49</x:v>
@@ -7063,7 +7066,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AO42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AP42" s="12" t="s">
         <x:v>49</x:v>
@@ -7072,10 +7075,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AR42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AS42" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AT42" s="12" t="s">
         <x:v>49</x:v>
@@ -7084,10 +7087,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AV42" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AW42" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AX42" s="12" t="s">
         <x:v>49</x:v>
@@ -7096,10 +7099,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AZ42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BA42" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB42" s="12" t="s">
         <x:v>49</x:v>
@@ -7108,230 +7111,230 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="BD42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BE42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="BF42" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG42" s="12">
-        <x:v>48</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="BH42" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="BI42" s="12">
-        <x:v>42</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="BJ42" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:62">
       <x:c r="A43" s="11" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="H43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I43" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="L43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M43" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="P43" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="R43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="S43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="T43" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="W43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="X43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AA43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AB43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AE43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AF43" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG43" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AI43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AJ43" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AM43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AN43" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO43" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AP43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AQ43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AR43" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS43" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AU43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AV43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AY43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AZ43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BA43" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BB43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BC43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="BD43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE43" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BF43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BG43" s="12">
-        <x:v>24</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH43" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI43" s="12">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BJ43" s="12" t="s">
-        <x:v>123</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:62">
       <x:c r="A44" s="11" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>138</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E44" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F44" s="12" t="s">
         <x:v>49</x:v>
@@ -7340,10 +7343,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H44" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I44" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J44" s="12" t="s">
         <x:v>49</x:v>
@@ -7352,10 +7355,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="L44" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M44" s="12" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="M44" s="12" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="N44" s="12" t="s">
         <x:v>49</x:v>
@@ -7364,10 +7367,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="P44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R44" s="12" t="s">
         <x:v>49</x:v>
@@ -7379,19 +7382,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="U44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="W44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="X44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z44" s="12" t="s">
         <x:v>49</x:v>
@@ -7400,10 +7403,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AB44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC44" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AD44" s="12" t="s">
         <x:v>49</x:v>
@@ -7412,10 +7415,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AF44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG44" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH44" s="12" t="s">
         <x:v>49</x:v>
@@ -7424,10 +7427,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AJ44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK44" s="12" t="s">
-        <x:v>126</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL44" s="12" t="s">
         <x:v>49</x:v>
@@ -7436,10 +7439,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AN44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP44" s="12" t="s">
         <x:v>49</x:v>
@@ -7448,10 +7451,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AR44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AT44" s="12" t="s">
         <x:v>49</x:v>
@@ -7460,10 +7463,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AV44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW44" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AX44" s="12" t="s">
         <x:v>49</x:v>
@@ -7472,10 +7475,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AZ44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA44" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BB44" s="12" t="s">
         <x:v>49</x:v>
@@ -7484,25 +7487,25 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="BD44" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BE44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF44" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG44" s="12">
-        <x:v>146</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BH44" s="12" t="s">
-        <x:v>139</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BI44" s="12">
-        <x:v>146</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BJ44" s="12" t="s">
-        <x:v>139</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:62">
@@ -7516,181 +7519,181 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="D45" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="H45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="L45" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M45" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="P45" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="R45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="S45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="T45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="W45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="X45" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AA45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AB45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AE45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF45" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG45" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AI45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AJ45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK45" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AM45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AN45" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AP45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AQ45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AR45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AU45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AV45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AY45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AZ45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BA45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BB45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BC45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="BD45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BF45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BG45" s="12">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH45" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI45" s="12">
-        <x:v>23</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BJ45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:62">
@@ -7707,7 +7710,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E46" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F46" s="12" t="s">
         <x:v>49</x:v>
@@ -7716,10 +7719,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H46" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J46" s="12" t="s">
         <x:v>49</x:v>
@@ -7728,10 +7731,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="L46" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M46" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N46" s="12" t="s">
         <x:v>49</x:v>
@@ -7740,10 +7743,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="P46" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q46" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R46" s="12" t="s">
         <x:v>49</x:v>
@@ -7764,10 +7767,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="X46" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y46" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z46" s="12" t="s">
         <x:v>49</x:v>
@@ -7779,7 +7782,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AC46" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AD46" s="12" t="s">
         <x:v>49</x:v>
@@ -7791,7 +7794,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AG46" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH46" s="12" t="s">
         <x:v>49</x:v>
@@ -7803,7 +7806,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AK46" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AL46" s="12" t="s">
         <x:v>49</x:v>
@@ -7815,7 +7818,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AO46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP46" s="12" t="s">
         <x:v>49</x:v>
@@ -7827,7 +7830,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AS46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AT46" s="12" t="s">
         <x:v>49</x:v>
@@ -7836,10 +7839,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AV46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AW46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX46" s="12" t="s">
         <x:v>49</x:v>
@@ -7848,10 +7851,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AZ46" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BA46" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BB46" s="12" t="s">
         <x:v>49</x:v>
@@ -7863,27 +7866,27 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BE46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF46" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG46" s="12">
-        <x:v>94</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BH46" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BI46" s="12">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="BJ46" s="12" t="s">
-        <x:v>143</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:62">
       <x:c r="A47" s="11" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B47" s="12" t="s">
         <x:v>47</x:v>
@@ -7892,10 +7895,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E47" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F47" s="12" t="s">
         <x:v>49</x:v>
@@ -7904,10 +7907,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="H47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J47" s="12" t="s">
         <x:v>49</x:v>
@@ -7916,10 +7919,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="M47" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N47" s="12" t="s">
         <x:v>49</x:v>
@@ -7928,10 +7931,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="P47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="Q47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R47" s="12" t="s">
         <x:v>49</x:v>
@@ -7940,22 +7943,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="T47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="X47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z47" s="12" t="s">
         <x:v>49</x:v>
@@ -7964,10 +7967,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AB47" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AC47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD47" s="12" t="s">
         <x:v>49</x:v>
@@ -7976,10 +7979,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AF47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AG47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH47" s="12" t="s">
         <x:v>49</x:v>
@@ -7988,10 +7991,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AJ47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AK47" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL47" s="12" t="s">
         <x:v>49</x:v>
@@ -8000,10 +8003,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AN47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AO47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP47" s="12" t="s">
         <x:v>49</x:v>
@@ -8012,7 +8015,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AR47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AS47" s="12" t="s">
         <x:v>49</x:v>
@@ -8024,10 +8027,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AV47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AW47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX47" s="12" t="s">
         <x:v>49</x:v>
@@ -8036,10 +8039,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AZ47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BA47" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB47" s="12" t="s">
         <x:v>49</x:v>
@@ -8048,42 +8051,42 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="BD47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BE47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF47" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG47" s="12">
-        <x:v>65</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH47" s="12" t="s">
-        <x:v>105</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI47" s="12">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BJ47" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:62">
       <x:c r="A48" s="11" t="s">
-        <x:v>145</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B48" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D48" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F48" s="12" t="s">
         <x:v>49</x:v>
@@ -8095,7 +8098,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J48" s="12" t="s">
         <x:v>49</x:v>
@@ -8104,10 +8107,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="L48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N48" s="12" t="s">
         <x:v>49</x:v>
@@ -8116,10 +8119,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="P48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R48" s="12" t="s">
         <x:v>49</x:v>
@@ -8128,13 +8131,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="T48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U48" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V48" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="W48" s="12">
         <x:v>36</x:v>
@@ -8143,7 +8146,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Y48" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z48" s="12" t="s">
         <x:v>49</x:v>
@@ -8152,10 +8155,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AB48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD48" s="12" t="s">
         <x:v>49</x:v>
@@ -8164,10 +8167,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AF48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG48" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH48" s="12" t="s">
         <x:v>49</x:v>
@@ -8176,10 +8179,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AJ48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK48" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL48" s="12" t="s">
         <x:v>49</x:v>
@@ -8188,10 +8191,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AN48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO48" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP48" s="12" t="s">
         <x:v>49</x:v>
@@ -8200,10 +8203,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AR48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS48" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AT48" s="12" t="s">
         <x:v>49</x:v>
@@ -8212,10 +8215,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AV48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW48" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX48" s="12" t="s">
         <x:v>49</x:v>
@@ -8224,10 +8227,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AZ48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA48" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BB48" s="12" t="s">
         <x:v>49</x:v>
@@ -8236,42 +8239,42 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="BD48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE48" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF48" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG48" s="12">
-        <x:v>155</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="BH48" s="12" t="s">
-        <x:v>146</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="BI48" s="12">
-        <x:v>143</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="BJ48" s="12" t="s">
-        <x:v>147</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:62">
       <x:c r="A49" s="11" t="s">
-        <x:v>148</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B49" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="D49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F49" s="12" t="s">
         <x:v>49</x:v>
@@ -8280,10 +8283,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="H49" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I49" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J49" s="12" t="s">
         <x:v>49</x:v>
@@ -8292,10 +8295,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="L49" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="M49" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N49" s="12" t="s">
         <x:v>49</x:v>
@@ -8304,10 +8307,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="P49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q49" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R49" s="12" t="s">
         <x:v>49</x:v>
@@ -8316,22 +8319,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="T49" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="U49" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V49" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="X49" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Z49" s="12" t="s">
         <x:v>49</x:v>
@@ -8340,10 +8343,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AB49" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AC49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AD49" s="12" t="s">
         <x:v>49</x:v>
@@ -8352,10 +8355,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AF49" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG49" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="AH49" s="12" t="s">
         <x:v>49</x:v>
@@ -8364,10 +8367,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AJ49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK49" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="AL49" s="12" t="s">
         <x:v>49</x:v>
@@ -8376,10 +8379,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AN49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AP49" s="12" t="s">
         <x:v>49</x:v>
@@ -8388,10 +8391,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AR49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT49" s="12" t="s">
         <x:v>49</x:v>
@@ -8400,10 +8403,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AV49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW49" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AX49" s="12" t="s">
         <x:v>49</x:v>
@@ -8412,10 +8415,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AZ49" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BA49" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BB49" s="12" t="s">
         <x:v>49</x:v>
@@ -8424,30 +8427,30 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="BD49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BE49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BF49" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG49" s="12">
-        <x:v>48</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="BH49" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="BI49" s="12">
-        <x:v>46</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="BJ49" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:62">
       <x:c r="A50" s="11" t="s">
-        <x:v>149</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B50" s="12" t="s">
         <x:v>47</x:v>
@@ -8456,10 +8459,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F50" s="12" t="s">
         <x:v>49</x:v>
@@ -8468,10 +8471,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="H50" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I50" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J50" s="12" t="s">
         <x:v>49</x:v>
@@ -8483,7 +8486,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="M50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N50" s="12" t="s">
         <x:v>49</x:v>
@@ -8495,7 +8498,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Q50" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R50" s="12" t="s">
         <x:v>49</x:v>
@@ -8504,13 +8507,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="T50" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U50" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="V50" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="W50" s="12">
         <x:v>38</x:v>
@@ -8528,7 +8531,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AB50" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC50" s="12" t="s">
         <x:v>52</x:v>
@@ -8540,7 +8543,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AF50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AG50" s="12" t="s">
         <x:v>54</x:v>
@@ -8552,10 +8555,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AJ50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK50" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL50" s="12" t="s">
         <x:v>49</x:v>
@@ -8579,7 +8582,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AS50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AT50" s="12" t="s">
         <x:v>49</x:v>
@@ -8588,10 +8591,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AV50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW50" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX50" s="12" t="s">
         <x:v>49</x:v>
@@ -8600,7 +8603,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AZ50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA50" s="12" t="s">
         <x:v>49</x:v>
@@ -8615,36 +8618,36 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE50" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BF50" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG50" s="12">
-        <x:v>34</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="BH50" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="BI50" s="12">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="BJ50" s="12" t="s">
-        <x:v>150</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:62">
       <x:c r="A51" s="11" t="s">
-        <x:v>151</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B51" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D51" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E51" s="12" t="s">
         <x:v>52</x:v>
@@ -8659,7 +8662,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="I51" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J51" s="12" t="s">
         <x:v>49</x:v>
@@ -8668,10 +8671,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="L51" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N51" s="12" t="s">
         <x:v>49</x:v>
@@ -8680,10 +8683,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="P51" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q51" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R51" s="12" t="s">
         <x:v>49</x:v>
@@ -8692,13 +8695,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="T51" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="W51" s="12">
         <x:v>39</x:v>
@@ -8707,7 +8710,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="Y51" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z51" s="12" t="s">
         <x:v>49</x:v>
@@ -8716,7 +8719,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AB51" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC51" s="12" t="s">
         <x:v>54</x:v>
@@ -8728,7 +8731,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AF51" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG51" s="12" t="s">
         <x:v>55</x:v>
@@ -8740,7 +8743,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AJ51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK51" s="12" t="s">
         <x:v>63</x:v>
@@ -8752,10 +8755,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AN51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO51" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP51" s="12" t="s">
         <x:v>49</x:v>
@@ -8764,10 +8767,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AR51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS51" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT51" s="12" t="s">
         <x:v>49</x:v>
@@ -8776,10 +8779,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AV51" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW51" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX51" s="12" t="s">
         <x:v>49</x:v>
@@ -8788,10 +8791,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AZ51" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA51" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BB51" s="12" t="s">
         <x:v>49</x:v>
@@ -8800,39 +8803,39 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="BD51" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE51" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF51" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG51" s="12">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="BH51" s="12" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="BI51" s="12">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BJ51" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:62">
       <x:c r="A52" s="11" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B52" s="12" t="s">
-        <x:v>138</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E52" s="12" t="s">
         <x:v>52</x:v>
@@ -8844,10 +8847,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J52" s="12" t="s">
         <x:v>49</x:v>
@@ -8856,10 +8859,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="L52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N52" s="12" t="s">
         <x:v>49</x:v>
@@ -8868,10 +8871,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="P52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q52" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R52" s="12" t="s">
         <x:v>49</x:v>
@@ -8880,22 +8883,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="T52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="W52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="X52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z52" s="12" t="s">
         <x:v>49</x:v>
@@ -8904,10 +8907,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AB52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AC52" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AD52" s="12" t="s">
         <x:v>49</x:v>
@@ -8916,10 +8919,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AF52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH52" s="12" t="s">
         <x:v>49</x:v>
@@ -8928,10 +8931,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AJ52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AL52" s="12" t="s">
         <x:v>49</x:v>
@@ -8940,10 +8943,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AN52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP52" s="12" t="s">
         <x:v>49</x:v>
@@ -8952,7 +8955,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AR52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS52" s="12" t="s">
         <x:v>49</x:v>
@@ -8964,10 +8967,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AV52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX52" s="12" t="s">
         <x:v>49</x:v>
@@ -8976,10 +8979,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AZ52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BB52" s="12" t="s">
         <x:v>49</x:v>
@@ -8988,33 +8991,33 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="BD52" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF52" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG52" s="12">
-        <x:v>5</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BH52" s="12" t="s">
-        <x:v>154</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BI52" s="12">
-        <x:v>5</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BJ52" s="12" t="s">
-        <x:v>154</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:62">
       <x:c r="A53" s="11" t="s">
-        <x:v>155</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B53" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C53" s="12">
         <x:v>41</x:v>
@@ -9023,7 +9026,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F53" s="12" t="s">
         <x:v>49</x:v>
@@ -9032,10 +9035,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H53" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I53" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J53" s="12" t="s">
         <x:v>49</x:v>
@@ -9044,10 +9047,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="L53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M53" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N53" s="12" t="s">
         <x:v>49</x:v>
@@ -9056,10 +9059,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="P53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Q53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="R53" s="12" t="s">
         <x:v>49</x:v>
@@ -9068,22 +9071,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="T53" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="U53" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V53" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="W53" s="12">
         <x:v>41</x:v>
       </x:c>
       <x:c r="X53" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z53" s="12" t="s">
         <x:v>49</x:v>
@@ -9095,7 +9098,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="AC53" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD53" s="12" t="s">
         <x:v>49</x:v>
@@ -9107,7 +9110,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AG53" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="AH53" s="12" t="s">
         <x:v>49</x:v>
@@ -9116,10 +9119,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AJ53" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK53" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL53" s="12" t="s">
         <x:v>49</x:v>
@@ -9128,10 +9131,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AN53" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AO53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AP53" s="12" t="s">
         <x:v>49</x:v>
@@ -9140,10 +9143,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AR53" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS53" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="AT53" s="12" t="s">
         <x:v>49</x:v>
@@ -9152,10 +9155,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AV53" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AW53" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AX53" s="12" t="s">
         <x:v>49</x:v>
@@ -9164,10 +9167,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AZ53" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BA53" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB53" s="12" t="s">
         <x:v>49</x:v>
@@ -9176,25 +9179,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="BD53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BE53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="BF53" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG53" s="12">
-        <x:v>44</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="BH53" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="BI53" s="12">
-        <x:v>38</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="BJ53" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:62">
@@ -9208,7 +9211,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="D54" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E54" s="12" t="s">
         <x:v>49</x:v>
@@ -9220,7 +9223,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H54" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I54" s="12" t="s">
         <x:v>52</x:v>
@@ -9232,10 +9235,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="M54" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N54" s="12" t="s">
         <x:v>49</x:v>
@@ -9244,10 +9247,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="P54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="Q54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R54" s="12" t="s">
         <x:v>49</x:v>
@@ -9256,22 +9259,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="T54" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="U54" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V54" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="X54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y54" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z54" s="12" t="s">
         <x:v>49</x:v>
@@ -9280,10 +9283,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AB54" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AC54" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD54" s="12" t="s">
         <x:v>49</x:v>
@@ -9292,10 +9295,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AF54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AG54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH54" s="12" t="s">
         <x:v>49</x:v>
@@ -9304,10 +9307,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AJ54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL54" s="12" t="s">
         <x:v>49</x:v>
@@ -9316,10 +9319,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AN54" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AO54" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP54" s="12" t="s">
         <x:v>49</x:v>
@@ -9328,10 +9331,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AR54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AS54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT54" s="12" t="s">
         <x:v>49</x:v>
@@ -9340,7 +9343,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AV54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AW54" s="12" t="s">
         <x:v>52</x:v>
@@ -9352,10 +9355,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AZ54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BA54" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB54" s="12" t="s">
         <x:v>49</x:v>
@@ -9364,30 +9367,30 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="BD54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BE54" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF54" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG54" s="12">
-        <x:v>53</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BH54" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="BI54" s="12">
-        <x:v>47</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BJ54" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:62">
       <x:c r="A55" s="11" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
         <x:v>47</x:v>
@@ -9396,10 +9399,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="D55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E55" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F55" s="12" t="s">
         <x:v>49</x:v>
@@ -9411,7 +9414,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="I55" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J55" s="12" t="s">
         <x:v>49</x:v>
@@ -9420,10 +9423,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M55" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N55" s="12" t="s">
         <x:v>49</x:v>
@@ -9432,7 +9435,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="P55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q55" s="12" t="s">
         <x:v>52</x:v>
@@ -9444,7 +9447,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="T55" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="U55" s="12" t="s">
         <x:v>52</x:v>
@@ -9456,10 +9459,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="X55" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y55" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z55" s="12" t="s">
         <x:v>49</x:v>
@@ -9468,10 +9471,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AB55" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC55" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD55" s="12" t="s">
         <x:v>49</x:v>
@@ -9480,10 +9483,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AF55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG55" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH55" s="12" t="s">
         <x:v>49</x:v>
@@ -9492,10 +9495,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AJ55" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK55" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AL55" s="12" t="s">
         <x:v>49</x:v>
@@ -9504,10 +9507,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AN55" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AO55" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP55" s="12" t="s">
         <x:v>49</x:v>
@@ -9516,10 +9519,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AR55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS55" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT55" s="12" t="s">
         <x:v>49</x:v>
@@ -9528,10 +9531,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AV55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AW55" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AX55" s="12" t="s">
         <x:v>49</x:v>
@@ -9540,10 +9543,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AZ55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BA55" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BB55" s="12" t="s">
         <x:v>49</x:v>
@@ -9552,30 +9555,30 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="BD55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BE55" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BF55" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG55" s="12">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BH55" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BI55" s="12">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="BJ55" s="12" t="s">
-        <x:v>110</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:62">
       <x:c r="A56" s="11" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B56" s="12" t="s">
         <x:v>47</x:v>
@@ -9584,7 +9587,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="D56" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E56" s="12" t="s">
         <x:v>49</x:v>
@@ -9596,10 +9599,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H56" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I56" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J56" s="12" t="s">
         <x:v>49</x:v>
@@ -9608,7 +9611,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="L56" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M56" s="12" t="s">
         <x:v>49</x:v>
@@ -9620,10 +9623,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="P56" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q56" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R56" s="12" t="s">
         <x:v>49</x:v>
@@ -9632,22 +9635,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="T56" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U56" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V56" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="W56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="X56" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y56" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Z56" s="12" t="s">
         <x:v>49</x:v>
@@ -9656,10 +9659,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AB56" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC56" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD56" s="12" t="s">
         <x:v>49</x:v>
@@ -9668,10 +9671,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AF56" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG56" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH56" s="12" t="s">
         <x:v>49</x:v>
@@ -9680,10 +9683,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AJ56" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK56" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AL56" s="12" t="s">
         <x:v>49</x:v>
@@ -9692,7 +9695,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AN56" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO56" s="12" t="s">
         <x:v>49</x:v>
@@ -9704,7 +9707,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AR56" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS56" s="12" t="s">
         <x:v>49</x:v>
@@ -9716,10 +9719,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AV56" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW56" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX56" s="12" t="s">
         <x:v>49</x:v>
@@ -9728,7 +9731,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AZ56" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA56" s="12" t="s">
         <x:v>49</x:v>
@@ -9740,42 +9743,42 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="BD56" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE56" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BF56" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG56" s="12">
-        <x:v>6</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="BH56" s="12" t="s">
-        <x:v>154</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BI56" s="12">
-        <x:v>6</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="BJ56" s="12" t="s">
-        <x:v>154</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:62">
       <x:c r="A57" s="11" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B57" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C57" s="12">
         <x:v>45</x:v>
       </x:c>
       <x:c r="D57" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F57" s="12" t="s">
         <x:v>49</x:v>
@@ -9784,10 +9787,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H57" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J57" s="12" t="s">
         <x:v>49</x:v>
@@ -9796,10 +9799,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L57" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N57" s="12" t="s">
         <x:v>49</x:v>
@@ -9808,10 +9811,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="P57" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R57" s="12" t="s">
         <x:v>49</x:v>
@@ -9820,22 +9823,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="T57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="U57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="W57" s="12">
         <x:v>45</x:v>
       </x:c>
       <x:c r="X57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Z57" s="12" t="s">
         <x:v>49</x:v>
@@ -9844,10 +9847,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AB57" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AC57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD57" s="12" t="s">
         <x:v>49</x:v>
@@ -9856,10 +9859,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AF57" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AG57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AH57" s="12" t="s">
         <x:v>49</x:v>
@@ -9868,10 +9871,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AJ57" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL57" s="12" t="s">
         <x:v>49</x:v>
@@ -9880,10 +9883,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AN57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AO57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AP57" s="12" t="s">
         <x:v>49</x:v>
@@ -9892,10 +9895,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AR57" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AS57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT57" s="12" t="s">
         <x:v>49</x:v>
@@ -9904,10 +9907,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AV57" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AX57" s="12" t="s">
         <x:v>49</x:v>
@@ -9916,10 +9919,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AZ57" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BA57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BB57" s="12" t="s">
         <x:v>49</x:v>
@@ -9928,30 +9931,30 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="BD57" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BE57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="BF57" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG57" s="12">
-        <x:v>0</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="BH57" s="12" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="BI57" s="12">
-        <x:v>0</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="BJ57" s="12" t="s">
-        <x:v>160</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:62">
       <x:c r="A58" s="11" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
         <x:v>47</x:v>
@@ -10128,21 +10131,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BH58" s="12" t="s">
-        <x:v>160</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI58" s="12">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BJ58" s="12" t="s">
-        <x:v>162</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:62">
       <x:c r="A59" s="11" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B59" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C59" s="12">
         <x:v>47</x:v>
@@ -10151,10 +10154,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G59" s="12">
         <x:v>47</x:v>
@@ -10163,10 +10166,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K59" s="12">
         <x:v>47</x:v>
@@ -10175,10 +10178,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="M59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="O59" s="12">
         <x:v>47</x:v>
@@ -10187,10 +10190,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="Q59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S59" s="12">
         <x:v>47</x:v>
@@ -10199,10 +10202,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="U59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W59" s="12">
         <x:v>47</x:v>
@@ -10211,10 +10214,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="Y59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA59" s="12">
         <x:v>47</x:v>
@@ -10223,10 +10226,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AC59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AD59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE59" s="12">
         <x:v>47</x:v>
@@ -10235,10 +10238,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AG59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AI59" s="12">
         <x:v>47</x:v>
@@ -10247,10 +10250,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AK59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM59" s="12">
         <x:v>47</x:v>
@@ -10259,10 +10262,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AO59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ59" s="12">
         <x:v>47</x:v>
@@ -10271,10 +10274,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AS59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU59" s="12">
         <x:v>47</x:v>
@@ -10283,10 +10286,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AW59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY59" s="12">
         <x:v>47</x:v>
@@ -10295,10 +10298,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="BA59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC59" s="12">
         <x:v>47</x:v>
@@ -10307,27 +10310,27 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="BE59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG59" s="12">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BH59" s="12" t="s">
-        <x:v>160</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="BI59" s="12">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BJ59" s="12" t="s">
-        <x:v>162</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:62">
       <x:c r="A60" s="11" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
         <x:v>47</x:v>
@@ -10336,25 +10339,25 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G60" s="12">
         <x:v>48</x:v>
       </x:c>
       <x:c r="H60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K60" s="12">
         <x:v>48</x:v>
@@ -10363,159 +10366,159 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="M60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="O60" s="12">
         <x:v>48</x:v>
       </x:c>
       <x:c r="P60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S60" s="12">
         <x:v>48</x:v>
       </x:c>
       <x:c r="T60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="W60" s="12">
         <x:v>48</x:v>
       </x:c>
       <x:c r="X60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA60" s="12">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AB60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AC60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE60" s="12">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AF60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AI60" s="12">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AJ60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AL60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM60" s="12">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AN60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ60" s="12">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AR60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AT60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU60" s="12">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AV60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY60" s="12">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AZ60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BB60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC60" s="12">
         <x:v>48</x:v>
       </x:c>
       <x:c r="BD60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BE60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG60" s="12">
-        <x:v>0</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="BH60" s="12" t="s">
-        <x:v>160</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="BI60" s="12">
-        <x:v>0</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="BJ60" s="12" t="s">
-        <x:v>162</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:62">
       <x:c r="A61" s="11" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B61" s="12" t="s">
         <x:v>47</x:v>
@@ -10524,186 +10527,186 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="D61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="H61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="L61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="O61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="P61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="T61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="V61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="W61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="X61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="AB61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AC61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="AF61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AI61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="AJ61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="AN61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="AR61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="AV61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="AZ61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BA61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BD61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BE61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BF61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG61" s="12">
-        <x:v>0</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="BH61" s="12" t="s">
-        <x:v>160</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="BI61" s="12">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BJ61" s="12" t="s">
-        <x:v>162</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:62">
       <x:c r="A62" s="11" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
         <x:v>47</x:v>
@@ -10712,270 +10715,270 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="H62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="L62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="O62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="P62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="T62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="U62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="W62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="X62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="Z62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AB62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AC62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AF62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AI62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AJ62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AN62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AR62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AV62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AZ62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BB62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="BD62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BE62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG62" s="12">
-        <x:v>0</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BH62" s="12" t="s">
-        <x:v>160</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="BI62" s="12">
-        <x:v>0</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="BJ62" s="12" t="s">
-        <x:v>162</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:62">
       <x:c r="A63" s="13" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B63" s="13" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C63" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D63" s="7"/>
       <x:c r="E63" s="7"/>
       <x:c r="F63" s="7"/>
       <x:c r="G63" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H63" s="7"/>
       <x:c r="I63" s="7"/>
       <x:c r="J63" s="7"/>
       <x:c r="K63" s="7" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="L63" s="7"/>
       <x:c r="M63" s="7"/>
       <x:c r="N63" s="7"/>
       <x:c r="O63" s="7" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="P63" s="7"/>
       <x:c r="Q63" s="7"/>
       <x:c r="R63" s="7"/>
       <x:c r="S63" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="T63" s="7"/>
       <x:c r="U63" s="7"/>
       <x:c r="V63" s="7"/>
       <x:c r="W63" s="7" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="X63" s="7"/>
       <x:c r="Y63" s="7"/>
       <x:c r="Z63" s="7"/>
       <x:c r="AA63" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="AB63" s="7"/>
       <x:c r="AC63" s="7"/>
       <x:c r="AD63" s="7"/>
       <x:c r="AE63" s="7" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="AF63" s="7"/>
       <x:c r="AG63" s="7"/>
       <x:c r="AH63" s="7"/>
       <x:c r="AI63" s="7" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="AJ63" s="7"/>
       <x:c r="AK63" s="7"/>
       <x:c r="AL63" s="7"/>
       <x:c r="AM63" s="7" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="AN63" s="7"/>
       <x:c r="AO63" s="7"/>
       <x:c r="AP63" s="7"/>
       <x:c r="AQ63" s="7" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="AR63" s="7"/>
       <x:c r="AS63" s="7"/>
       <x:c r="AT63" s="7"/>
       <x:c r="AU63" s="7" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="AV63" s="7"/>
       <x:c r="AW63" s="7"/>
       <x:c r="AX63" s="7"/>
       <x:c r="AY63" s="7" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="AZ63" s="7"/>
       <x:c r="BA63" s="7"/>
       <x:c r="BB63" s="7"/>
       <x:c r="BC63" s="7" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="BD63" s="7"/>
       <x:c r="BE63" s="7"/>
@@ -10987,37 +10990,37 @@
     </x:row>
     <x:row r="65" spans="1:62">
       <x:c r="A65" s="14" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:62">
       <x:c r="A66" s="13" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:62">
       <x:c r="A67" s="13" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:62">
       <x:c r="A68" s="13" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:62">
       <x:c r="A69" s="13" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:62">
       <x:c r="A70" s="13" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:62">
       <x:c r="A71" s="13" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
